--- a/artfynd/A 22466-2025 artfynd.xlsx
+++ b/artfynd/A 22466-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127102996</v>
+        <v>127109996</v>
       </c>
       <c r="B2" t="n">
-        <v>80083</v>
+        <v>57657</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Svartabborrtjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>591964</v>
+        <v>592025</v>
       </c>
       <c r="R2" t="n">
-        <v>6984904</v>
+        <v>6984843</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127109996</v>
+        <v>127102996</v>
       </c>
       <c r="B3" t="n">
-        <v>57657</v>
+        <v>80114</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,39 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Svartabborrtjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>592025</v>
+        <v>591964</v>
       </c>
       <c r="R3" t="n">
-        <v>6984843</v>
+        <v>6984904</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -848,11 +853,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-02</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -882,7 +882,7 @@
         <v>127103005</v>
       </c>
       <c r="B4" t="n">
-        <v>80083</v>
+        <v>80114</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -976,32 +976,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127102978</v>
+        <v>127103004</v>
       </c>
       <c r="B5" t="n">
-        <v>80112</v>
+        <v>80114</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1011,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>592067</v>
+        <v>591992</v>
       </c>
       <c r="R5" t="n">
-        <v>6984718</v>
+        <v>6984613</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1073,32 +1073,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127103004</v>
+        <v>127102978</v>
       </c>
       <c r="B6" t="n">
-        <v>80083</v>
+        <v>80143</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1108,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>591992</v>
+        <v>592067</v>
       </c>
       <c r="R6" t="n">
-        <v>6984613</v>
+        <v>6984718</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1275,7 +1275,7 @@
         <v>127102988</v>
       </c>
       <c r="B8" t="n">
-        <v>97239</v>
+        <v>97314</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>127103030</v>
       </c>
       <c r="B10" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         <v>127103029</v>
       </c>
       <c r="B11" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1780,7 +1780,7 @@
         <v>127111357</v>
       </c>
       <c r="B13" t="n">
-        <v>80083</v>
+        <v>80114</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1877,7 +1877,7 @@
         <v>127103033</v>
       </c>
       <c r="B14" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 22466-2025 artfynd.xlsx
+++ b/artfynd/A 22466-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127109996</v>
+        <v>127102996</v>
       </c>
       <c r="B2" t="n">
-        <v>57657</v>
+        <v>80117</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,39 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Svartabborrtjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>592025</v>
+        <v>591964</v>
       </c>
       <c r="R2" t="n">
-        <v>6984843</v>
+        <v>6984904</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-08-02</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127102996</v>
+        <v>127109996</v>
       </c>
       <c r="B3" t="n">
-        <v>80114</v>
+        <v>57657</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,34 +783,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Svartabborrtjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>591964</v>
+        <v>592025</v>
       </c>
       <c r="R3" t="n">
-        <v>6984904</v>
+        <v>6984843</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,6 +848,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -882,7 +882,7 @@
         <v>127103005</v>
       </c>
       <c r="B4" t="n">
-        <v>80114</v>
+        <v>80117</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -976,32 +976,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127103004</v>
+        <v>127102978</v>
       </c>
       <c r="B5" t="n">
-        <v>80114</v>
+        <v>80146</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1011,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>591992</v>
+        <v>592067</v>
       </c>
       <c r="R5" t="n">
-        <v>6984613</v>
+        <v>6984718</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1073,32 +1073,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127102978</v>
+        <v>127103004</v>
       </c>
       <c r="B6" t="n">
-        <v>80143</v>
+        <v>80117</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1108,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>592067</v>
+        <v>591992</v>
       </c>
       <c r="R6" t="n">
-        <v>6984718</v>
+        <v>6984613</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1275,7 +1275,7 @@
         <v>127102988</v>
       </c>
       <c r="B8" t="n">
-        <v>97314</v>
+        <v>97320</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1369,10 +1369,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127110089</v>
+        <v>127103030</v>
       </c>
       <c r="B9" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1380,39 +1380,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Gullabborrtjärnen, Jmt</t>
+          <t>Svartabborrtjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>592020</v>
+        <v>592044</v>
       </c>
       <c r="R9" t="n">
-        <v>6984798</v>
+        <v>6984706</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1445,11 +1440,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-02</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1476,10 +1466,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127103030</v>
+        <v>127103029</v>
       </c>
       <c r="B10" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1511,10 +1501,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>592044</v>
+        <v>591934</v>
       </c>
       <c r="R10" t="n">
-        <v>6984706</v>
+        <v>6984614</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1573,10 +1563,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127103029</v>
+        <v>127110089</v>
       </c>
       <c r="B11" t="n">
-        <v>79011</v>
+        <v>57657</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1584,34 +1574,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Svartabborrtjärnbäcken, Jmt</t>
+          <t>Gullabborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>591934</v>
+        <v>592020</v>
       </c>
       <c r="R11" t="n">
-        <v>6984614</v>
+        <v>6984798</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1644,6 +1639,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1780,7 +1780,7 @@
         <v>127111357</v>
       </c>
       <c r="B13" t="n">
-        <v>80114</v>
+        <v>80117</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1877,7 +1877,7 @@
         <v>127103033</v>
       </c>
       <c r="B14" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 22466-2025 artfynd.xlsx
+++ b/artfynd/A 22466-2025 artfynd.xlsx
@@ -976,32 +976,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127102978</v>
+        <v>127103004</v>
       </c>
       <c r="B5" t="n">
-        <v>80146</v>
+        <v>80117</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1011,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>592067</v>
+        <v>591992</v>
       </c>
       <c r="R5" t="n">
-        <v>6984718</v>
+        <v>6984613</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1073,32 +1073,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127103004</v>
+        <v>127102978</v>
       </c>
       <c r="B6" t="n">
-        <v>80117</v>
+        <v>80146</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1108,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>591992</v>
+        <v>592067</v>
       </c>
       <c r="R6" t="n">
-        <v>6984613</v>
+        <v>6984718</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 22466-2025 artfynd.xlsx
+++ b/artfynd/A 22466-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1275,7 +1275,7 @@
         <v>127102988</v>
       </c>
       <c r="B8" t="n">
-        <v>97320</v>
+        <v>97321</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2085,6 +2085,210 @@
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>127404697</v>
+      </c>
+      <c r="B16" t="n">
+        <v>82855</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Svartabborrtjärnbäcken, Svartabborrtjärnbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>592016</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6984649</v>
+      </c>
+      <c r="S16" t="n">
+        <v>15</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>127404764</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57657</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Svartabborrtjärnbäcken, Svartabborrtjärnbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>592010</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6984626</v>
+      </c>
+      <c r="S17" t="n">
+        <v>15</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack, gran</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 22466-2025 artfynd.xlsx
+++ b/artfynd/A 22466-2025 artfynd.xlsx
@@ -1369,7 +1369,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127103030</v>
+        <v>127103029</v>
       </c>
       <c r="B9" t="n">
         <v>79014</v>
@@ -1404,10 +1404,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>592044</v>
+        <v>591934</v>
       </c>
       <c r="R9" t="n">
-        <v>6984706</v>
+        <v>6984614</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1466,10 +1466,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127103029</v>
+        <v>127110089</v>
       </c>
       <c r="B10" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1477,34 +1477,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Svartabborrtjärnbäcken, Jmt</t>
+          <t>Gullabborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>591934</v>
+        <v>592020</v>
       </c>
       <c r="R10" t="n">
-        <v>6984614</v>
+        <v>6984798</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1537,6 +1542,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1563,10 +1573,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127110089</v>
+        <v>127103030</v>
       </c>
       <c r="B11" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1574,39 +1584,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Gullabborrtjärnen, Jmt</t>
+          <t>Svartabborrtjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>592020</v>
+        <v>592044</v>
       </c>
       <c r="R11" t="n">
-        <v>6984798</v>
+        <v>6984706</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1639,11 +1644,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-08-02</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 22466-2025 artfynd.xlsx
+++ b/artfynd/A 22466-2025 artfynd.xlsx
@@ -1369,7 +1369,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127103029</v>
+        <v>127103030</v>
       </c>
       <c r="B9" t="n">
         <v>79014</v>
@@ -1404,10 +1404,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>591934</v>
+        <v>592044</v>
       </c>
       <c r="R9" t="n">
-        <v>6984614</v>
+        <v>6984706</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1466,10 +1466,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127110089</v>
+        <v>127103029</v>
       </c>
       <c r="B10" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1477,39 +1477,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Gullabborrtjärnen, Jmt</t>
+          <t>Svartabborrtjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>592020</v>
+        <v>591934</v>
       </c>
       <c r="R10" t="n">
-        <v>6984798</v>
+        <v>6984614</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1542,11 +1537,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-02</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1573,10 +1563,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127103030</v>
+        <v>127110089</v>
       </c>
       <c r="B11" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1584,34 +1574,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Svartabborrtjärnbäcken, Jmt</t>
+          <t>Gullabborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>592044</v>
+        <v>592020</v>
       </c>
       <c r="R11" t="n">
-        <v>6984706</v>
+        <v>6984798</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1644,6 +1639,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 22466-2025 artfynd.xlsx
+++ b/artfynd/A 22466-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127102996</v>
       </c>
       <c r="B2" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127109996</v>
       </c>
       <c r="B3" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>127103005</v>
       </c>
       <c r="B4" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>127103004</v>
       </c>
       <c r="B5" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>127102978</v>
       </c>
       <c r="B6" t="n">
-        <v>80146</v>
+        <v>80150</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>127110231</v>
       </c>
       <c r="B7" t="n">
-        <v>58027</v>
+        <v>58031</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         <v>127102988</v>
       </c>
       <c r="B8" t="n">
-        <v>97321</v>
+        <v>97325</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
         <v>127103030</v>
       </c>
       <c r="B9" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         <v>127103029</v>
       </c>
       <c r="B10" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>127110089</v>
       </c>
       <c r="B11" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1673,7 +1673,7 @@
         <v>127098105</v>
       </c>
       <c r="B12" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1780,7 +1780,7 @@
         <v>127111357</v>
       </c>
       <c r="B13" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1877,7 +1877,7 @@
         <v>127103033</v>
       </c>
       <c r="B14" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
         <v>127093150</v>
       </c>
       <c r="B15" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
         <v>127404697</v>
       </c>
       <c r="B16" t="n">
-        <v>82855</v>
+        <v>82859</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2187,7 +2187,7 @@
         <v>127404764</v>
       </c>
       <c r="B17" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 22466-2025 artfynd.xlsx
+++ b/artfynd/A 22466-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127102996</v>
+        <v>127109996</v>
       </c>
       <c r="B2" t="n">
-        <v>80121</v>
+        <v>57661</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Svartabborrtjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>591964</v>
+        <v>592025</v>
       </c>
       <c r="R2" t="n">
-        <v>6984904</v>
+        <v>6984843</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127109996</v>
+        <v>127102996</v>
       </c>
       <c r="B3" t="n">
-        <v>57661</v>
+        <v>80121</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,39 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Svartabborrtjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>592025</v>
+        <v>591964</v>
       </c>
       <c r="R3" t="n">
-        <v>6984843</v>
+        <v>6984904</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -848,11 +853,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-02</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 22466-2025 artfynd.xlsx
+++ b/artfynd/A 22466-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127109996</v>
+        <v>127102996</v>
       </c>
       <c r="B2" t="n">
-        <v>57661</v>
+        <v>80121</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,39 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Svartabborrtjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>592025</v>
+        <v>591964</v>
       </c>
       <c r="R2" t="n">
-        <v>6984843</v>
+        <v>6984904</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-08-02</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127102996</v>
+        <v>127109996</v>
       </c>
       <c r="B3" t="n">
-        <v>80121</v>
+        <v>57661</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,34 +783,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Svartabborrtjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>591964</v>
+        <v>592025</v>
       </c>
       <c r="R3" t="n">
-        <v>6984904</v>
+        <v>6984843</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,6 +848,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 22466-2025 artfynd.xlsx
+++ b/artfynd/A 22466-2025 artfynd.xlsx
@@ -976,32 +976,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127103004</v>
+        <v>127102978</v>
       </c>
       <c r="B5" t="n">
-        <v>80121</v>
+        <v>80150</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1011,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>591992</v>
+        <v>592067</v>
       </c>
       <c r="R5" t="n">
-        <v>6984613</v>
+        <v>6984718</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1073,32 +1073,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127102978</v>
+        <v>127103004</v>
       </c>
       <c r="B6" t="n">
-        <v>80150</v>
+        <v>80121</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1108,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>592067</v>
+        <v>591992</v>
       </c>
       <c r="R6" t="n">
-        <v>6984718</v>
+        <v>6984613</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 22466-2025 artfynd.xlsx
+++ b/artfynd/A 22466-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127102996</v>
+        <v>127109996</v>
       </c>
       <c r="B2" t="n">
-        <v>80121</v>
+        <v>57663</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Svartabborrtjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>591964</v>
+        <v>592025</v>
       </c>
       <c r="R2" t="n">
-        <v>6984904</v>
+        <v>6984843</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127109996</v>
+        <v>127102996</v>
       </c>
       <c r="B3" t="n">
-        <v>57661</v>
+        <v>80123</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,39 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Svartabborrtjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>592025</v>
+        <v>591964</v>
       </c>
       <c r="R3" t="n">
-        <v>6984843</v>
+        <v>6984904</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -848,11 +853,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-02</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -882,7 +882,7 @@
         <v>127103005</v>
       </c>
       <c r="B4" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -976,32 +976,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127102978</v>
+        <v>127103004</v>
       </c>
       <c r="B5" t="n">
-        <v>80150</v>
+        <v>80123</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1011,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>592067</v>
+        <v>591992</v>
       </c>
       <c r="R5" t="n">
-        <v>6984718</v>
+        <v>6984613</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1073,32 +1073,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127103004</v>
+        <v>127102978</v>
       </c>
       <c r="B6" t="n">
-        <v>80121</v>
+        <v>80152</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1108,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>591992</v>
+        <v>592067</v>
       </c>
       <c r="R6" t="n">
-        <v>6984613</v>
+        <v>6984718</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,7 +1173,7 @@
         <v>127110231</v>
       </c>
       <c r="B7" t="n">
-        <v>58031</v>
+        <v>58033</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         <v>127102988</v>
       </c>
       <c r="B8" t="n">
-        <v>97325</v>
+        <v>97327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
         <v>127103030</v>
       </c>
       <c r="B9" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         <v>127103029</v>
       </c>
       <c r="B10" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>127110089</v>
       </c>
       <c r="B11" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1673,7 +1673,7 @@
         <v>127098105</v>
       </c>
       <c r="B12" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1780,7 +1780,7 @@
         <v>127111357</v>
       </c>
       <c r="B13" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1877,7 +1877,7 @@
         <v>127103033</v>
       </c>
       <c r="B14" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
         <v>127093150</v>
       </c>
       <c r="B15" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
         <v>127404697</v>
       </c>
       <c r="B16" t="n">
-        <v>82859</v>
+        <v>82861</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2187,7 +2187,7 @@
         <v>127404764</v>
       </c>
       <c r="B17" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 22466-2025 artfynd.xlsx
+++ b/artfynd/A 22466-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127109996</v>
+        <v>127102996</v>
       </c>
       <c r="B2" t="n">
-        <v>57663</v>
+        <v>80123</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,39 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Svartabborrtjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>592025</v>
+        <v>591964</v>
       </c>
       <c r="R2" t="n">
-        <v>6984843</v>
+        <v>6984904</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-08-02</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127102996</v>
+        <v>127109996</v>
       </c>
       <c r="B3" t="n">
-        <v>80123</v>
+        <v>57663</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,34 +783,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Svartabborrtjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>591964</v>
+        <v>592025</v>
       </c>
       <c r="R3" t="n">
-        <v>6984904</v>
+        <v>6984843</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,6 +848,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 22466-2025 artfynd.xlsx
+++ b/artfynd/A 22466-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127102996</v>
+        <v>127109996</v>
       </c>
       <c r="B2" t="n">
-        <v>80123</v>
+        <v>57663</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Svartabborrtjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>591964</v>
+        <v>592025</v>
       </c>
       <c r="R2" t="n">
-        <v>6984904</v>
+        <v>6984843</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127109996</v>
+        <v>127102996</v>
       </c>
       <c r="B3" t="n">
-        <v>57663</v>
+        <v>80123</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,39 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Svartabborrtjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>592025</v>
+        <v>591964</v>
       </c>
       <c r="R3" t="n">
-        <v>6984843</v>
+        <v>6984904</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -848,11 +853,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-02</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 22466-2025 artfynd.xlsx
+++ b/artfynd/A 22466-2025 artfynd.xlsx
@@ -1275,7 +1275,7 @@
         <v>127102988</v>
       </c>
       <c r="B8" t="n">
-        <v>97327</v>
+        <v>97333</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1369,10 +1369,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127103030</v>
+        <v>127110089</v>
       </c>
       <c r="B9" t="n">
-        <v>79020</v>
+        <v>57663</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1380,34 +1380,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Svartabborrtjärnbäcken, Jmt</t>
+          <t>Gullabborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>592044</v>
+        <v>592020</v>
       </c>
       <c r="R9" t="n">
-        <v>6984706</v>
+        <v>6984798</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1440,6 +1445,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1466,7 +1476,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127103029</v>
+        <v>127103030</v>
       </c>
       <c r="B10" t="n">
         <v>79020</v>
@@ -1501,10 +1511,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>591934</v>
+        <v>592044</v>
       </c>
       <c r="R10" t="n">
-        <v>6984614</v>
+        <v>6984706</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1563,10 +1573,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127110089</v>
+        <v>127103029</v>
       </c>
       <c r="B11" t="n">
-        <v>57663</v>
+        <v>79020</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1574,39 +1584,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Gullabborrtjärnen, Jmt</t>
+          <t>Svartabborrtjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>592020</v>
+        <v>591934</v>
       </c>
       <c r="R11" t="n">
-        <v>6984798</v>
+        <v>6984614</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1639,11 +1644,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-08-02</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 22466-2025 artfynd.xlsx
+++ b/artfynd/A 22466-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127109996</v>
+        <v>127102996</v>
       </c>
       <c r="B2" t="n">
-        <v>57663</v>
+        <v>80126</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,39 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Svartabborrtjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>592025</v>
+        <v>591964</v>
       </c>
       <c r="R2" t="n">
-        <v>6984843</v>
+        <v>6984904</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-08-02</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127102996</v>
+        <v>127109996</v>
       </c>
       <c r="B3" t="n">
-        <v>80123</v>
+        <v>57666</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,34 +783,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Svartabborrtjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>591964</v>
+        <v>592025</v>
       </c>
       <c r="R3" t="n">
-        <v>6984904</v>
+        <v>6984843</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,6 +848,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -882,7 +882,7 @@
         <v>127103005</v>
       </c>
       <c r="B4" t="n">
-        <v>80123</v>
+        <v>80126</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>127103004</v>
       </c>
       <c r="B5" t="n">
-        <v>80123</v>
+        <v>80126</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>127102978</v>
       </c>
       <c r="B6" t="n">
-        <v>80152</v>
+        <v>80155</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>127110231</v>
       </c>
       <c r="B7" t="n">
-        <v>58033</v>
+        <v>58036</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         <v>127102988</v>
       </c>
       <c r="B8" t="n">
-        <v>97333</v>
+        <v>97336</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1369,10 +1369,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127110089</v>
+        <v>127103030</v>
       </c>
       <c r="B9" t="n">
-        <v>57663</v>
+        <v>79023</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1380,39 +1380,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Gullabborrtjärnen, Jmt</t>
+          <t>Svartabborrtjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>592020</v>
+        <v>592044</v>
       </c>
       <c r="R9" t="n">
-        <v>6984798</v>
+        <v>6984706</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1445,11 +1440,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-02</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1476,10 +1466,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127103030</v>
+        <v>127103029</v>
       </c>
       <c r="B10" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1511,10 +1501,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>592044</v>
+        <v>591934</v>
       </c>
       <c r="R10" t="n">
-        <v>6984706</v>
+        <v>6984614</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1573,10 +1563,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127103029</v>
+        <v>127110089</v>
       </c>
       <c r="B11" t="n">
-        <v>79020</v>
+        <v>57666</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1584,34 +1574,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Svartabborrtjärnbäcken, Jmt</t>
+          <t>Gullabborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>591934</v>
+        <v>592020</v>
       </c>
       <c r="R11" t="n">
-        <v>6984614</v>
+        <v>6984798</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1644,6 +1639,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1673,7 +1673,7 @@
         <v>127098105</v>
       </c>
       <c r="B12" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1780,7 +1780,7 @@
         <v>127111357</v>
       </c>
       <c r="B13" t="n">
-        <v>80123</v>
+        <v>80126</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1877,7 +1877,7 @@
         <v>127103033</v>
       </c>
       <c r="B14" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
         <v>127093150</v>
       </c>
       <c r="B15" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
         <v>127404697</v>
       </c>
       <c r="B16" t="n">
-        <v>82861</v>
+        <v>82864</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2187,7 +2187,7 @@
         <v>127404764</v>
       </c>
       <c r="B17" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 22466-2025 artfynd.xlsx
+++ b/artfynd/A 22466-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127102996</v>
+        <v>127109996</v>
       </c>
       <c r="B2" t="n">
-        <v>80126</v>
+        <v>57672</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Svartabborrtjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>591964</v>
+        <v>592025</v>
       </c>
       <c r="R2" t="n">
-        <v>6984904</v>
+        <v>6984843</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127109996</v>
+        <v>127102996</v>
       </c>
       <c r="B3" t="n">
-        <v>57666</v>
+        <v>80132</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,39 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Svartabborrtjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>592025</v>
+        <v>591964</v>
       </c>
       <c r="R3" t="n">
-        <v>6984843</v>
+        <v>6984904</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -848,11 +853,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-02</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -882,7 +882,7 @@
         <v>127103005</v>
       </c>
       <c r="B4" t="n">
-        <v>80126</v>
+        <v>80132</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>127103004</v>
       </c>
       <c r="B5" t="n">
-        <v>80126</v>
+        <v>80132</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>127102978</v>
       </c>
       <c r="B6" t="n">
-        <v>80155</v>
+        <v>80161</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>127110231</v>
       </c>
       <c r="B7" t="n">
-        <v>58036</v>
+        <v>58042</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         <v>127102988</v>
       </c>
       <c r="B8" t="n">
-        <v>97336</v>
+        <v>97344</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
         <v>127103030</v>
       </c>
       <c r="B9" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         <v>127103029</v>
       </c>
       <c r="B10" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>127110089</v>
       </c>
       <c r="B11" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1673,7 +1673,7 @@
         <v>127098105</v>
       </c>
       <c r="B12" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1780,7 +1780,7 @@
         <v>127111357</v>
       </c>
       <c r="B13" t="n">
-        <v>80126</v>
+        <v>80132</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1877,7 +1877,7 @@
         <v>127103033</v>
       </c>
       <c r="B14" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
         <v>127093150</v>
       </c>
       <c r="B15" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
         <v>127404697</v>
       </c>
       <c r="B16" t="n">
-        <v>82864</v>
+        <v>82870</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2187,7 +2187,7 @@
         <v>127404764</v>
       </c>
       <c r="B17" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 22466-2025 artfynd.xlsx
+++ b/artfynd/A 22466-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2289,6 +2289,289 @@
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>129431314</v>
+      </c>
+      <c r="B18" t="n">
+        <v>91841</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>658</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Ödingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>591984</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6984890</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>129431313</v>
+      </c>
+      <c r="B19" t="n">
+        <v>91563</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Ödingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>591996</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6984775</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>129431315</v>
+      </c>
+      <c r="B20" t="n">
+        <v>91563</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Ödingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>591986</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6984894</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 22466-2025 artfynd.xlsx
+++ b/artfynd/A 22466-2025 artfynd.xlsx
@@ -2291,10 +2291,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129431314</v>
+        <v>129431313</v>
       </c>
       <c r="B18" t="n">
-        <v>91841</v>
+        <v>91565</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2302,23 +2302,19 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2326,10 +2322,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>591984</v>
+        <v>591996</v>
       </c>
       <c r="R18" t="n">
-        <v>6984890</v>
+        <v>6984775</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2388,10 +2384,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129431313</v>
+        <v>129431314</v>
       </c>
       <c r="B19" t="n">
-        <v>91563</v>
+        <v>91843</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2399,19 +2395,23 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr"/>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2419,10 +2419,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>591996</v>
+        <v>591984</v>
       </c>
       <c r="R19" t="n">
-        <v>6984775</v>
+        <v>6984890</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2484,7 +2484,7 @@
         <v>129431315</v>
       </c>
       <c r="B20" t="n">
-        <v>91563</v>
+        <v>91565</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 22466-2025 artfynd.xlsx
+++ b/artfynd/A 22466-2025 artfynd.xlsx
@@ -2291,10 +2291,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129431313</v>
+        <v>129431314</v>
       </c>
       <c r="B18" t="n">
-        <v>91565</v>
+        <v>91847</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2302,19 +2302,23 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2322,10 +2326,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>591996</v>
+        <v>591984</v>
       </c>
       <c r="R18" t="n">
-        <v>6984775</v>
+        <v>6984890</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2384,10 +2388,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129431314</v>
+        <v>129431313</v>
       </c>
       <c r="B19" t="n">
-        <v>91843</v>
+        <v>91569</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2395,23 +2399,19 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2419,10 +2419,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>591984</v>
+        <v>591996</v>
       </c>
       <c r="R19" t="n">
-        <v>6984890</v>
+        <v>6984775</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2484,7 +2484,7 @@
         <v>129431315</v>
       </c>
       <c r="B20" t="n">
-        <v>91565</v>
+        <v>91569</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 22466-2025 artfynd.xlsx
+++ b/artfynd/A 22466-2025 artfynd.xlsx
@@ -2291,10 +2291,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129431314</v>
+        <v>129431313</v>
       </c>
       <c r="B18" t="n">
-        <v>91847</v>
+        <v>91570</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2302,23 +2302,19 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2326,10 +2322,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>591984</v>
+        <v>591996</v>
       </c>
       <c r="R18" t="n">
-        <v>6984890</v>
+        <v>6984775</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2388,10 +2384,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129431313</v>
+        <v>129431314</v>
       </c>
       <c r="B19" t="n">
-        <v>91569</v>
+        <v>91848</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2399,19 +2395,23 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr"/>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2419,10 +2419,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>591996</v>
+        <v>591984</v>
       </c>
       <c r="R19" t="n">
-        <v>6984775</v>
+        <v>6984890</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2484,7 +2484,7 @@
         <v>129431315</v>
       </c>
       <c r="B20" t="n">
-        <v>91569</v>
+        <v>91570</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 22466-2025 artfynd.xlsx
+++ b/artfynd/A 22466-2025 artfynd.xlsx
@@ -2294,7 +2294,7 @@
         <v>129431313</v>
       </c>
       <c r="B18" t="n">
-        <v>91570</v>
+        <v>91573</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         <v>129431314</v>
       </c>
       <c r="B19" t="n">
-        <v>91848</v>
+        <v>91851</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>129431315</v>
       </c>
       <c r="B20" t="n">
-        <v>91570</v>
+        <v>91573</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 22466-2025 artfynd.xlsx
+++ b/artfynd/A 22466-2025 artfynd.xlsx
@@ -2291,10 +2291,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129431313</v>
+        <v>129431314</v>
       </c>
       <c r="B18" t="n">
-        <v>91573</v>
+        <v>91851</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2302,19 +2302,23 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2322,10 +2326,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>591996</v>
+        <v>591984</v>
       </c>
       <c r="R18" t="n">
-        <v>6984775</v>
+        <v>6984890</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2384,10 +2388,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129431314</v>
+        <v>129431313</v>
       </c>
       <c r="B19" t="n">
-        <v>91851</v>
+        <v>91573</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2395,23 +2399,19 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2419,10 +2419,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>591984</v>
+        <v>591996</v>
       </c>
       <c r="R19" t="n">
-        <v>6984890</v>
+        <v>6984775</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>

--- a/artfynd/A 22466-2025 artfynd.xlsx
+++ b/artfynd/A 22466-2025 artfynd.xlsx
@@ -2291,10 +2291,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129431314</v>
+        <v>129431313</v>
       </c>
       <c r="B18" t="n">
-        <v>91851</v>
+        <v>91573</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2302,23 +2302,19 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2326,10 +2322,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>591984</v>
+        <v>591996</v>
       </c>
       <c r="R18" t="n">
-        <v>6984890</v>
+        <v>6984775</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2388,10 +2384,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129431313</v>
+        <v>129431314</v>
       </c>
       <c r="B19" t="n">
-        <v>91573</v>
+        <v>91851</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2399,19 +2395,23 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr"/>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2419,10 +2419,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>591996</v>
+        <v>591984</v>
       </c>
       <c r="R19" t="n">
-        <v>6984775</v>
+        <v>6984890</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>

--- a/artfynd/A 22466-2025 artfynd.xlsx
+++ b/artfynd/A 22466-2025 artfynd.xlsx
@@ -2294,7 +2294,7 @@
         <v>129431314</v>
       </c>
       <c r="B18" t="n">
-        <v>91851</v>
+        <v>91879</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2391,7 +2391,7 @@
         <v>129431313</v>
       </c>
       <c r="B19" t="n">
-        <v>91573</v>
+        <v>91601</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>129431315</v>
       </c>
       <c r="B20" t="n">
-        <v>91573</v>
+        <v>91601</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
